--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI Project\finto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B97CDAB-89E4-48E7-A847-0CDD6E002EAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4568A59-A63E-4061-8271-A89337F44B96}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="11940" xr2:uid="{D4F2BFD6-B7A6-478A-AE74-1A475FB44544}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -52,15 +52,6 @@
   </si>
   <si>
     <t>Average Price</t>
-  </si>
-  <si>
-    <t>Previous Closing Price</t>
-  </si>
-  <si>
-    <t>Unrealized P&amp;L</t>
-  </si>
-  <si>
-    <t>Unrealized P&amp;L Pct.</t>
   </si>
   <si>
     <t/>
@@ -592,13 +583,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A32E8FB-6A9D-42D3-A92C-71F0DF18353C}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="6" max="6" width="57.140625" customWidth="1"/>
+    <col min="7" max="7" width="57.5703125" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,25 +621,16 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -664,28 +650,16 @@
       <c r="I2" s="2">
         <v>380.75</v>
       </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -705,28 +679,16 @@
       <c r="I3" s="2">
         <v>1012.6</v>
       </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -746,28 +708,16 @@
       <c r="I4" s="2">
         <v>195.4</v>
       </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -787,28 +737,16 @@
       <c r="I5" s="2">
         <v>486</v>
       </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -828,28 +766,16 @@
       <c r="I6" s="2">
         <v>431.15</v>
       </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -869,28 +795,16 @@
       <c r="I7" s="2">
         <v>3342.2</v>
       </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -910,28 +824,16 @@
       <c r="I8" s="2">
         <v>310.7</v>
       </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -951,28 +853,16 @@
       <c r="I9" s="2">
         <v>114</v>
       </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -992,28 +882,16 @@
       <c r="I10" s="2">
         <v>202</v>
       </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1033,28 +911,16 @@
       <c r="I11" s="2">
         <v>3408.75</v>
       </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1074,28 +940,16 @@
       <c r="I12" s="2">
         <v>41.62</v>
       </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -1115,28 +969,16 @@
       <c r="I13" s="2">
         <v>321</v>
       </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1156,28 +998,16 @@
       <c r="I14" s="2">
         <v>288.3</v>
       </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D15" s="2">
         <v>341</v>
@@ -1197,28 +1027,16 @@
       <c r="I15" s="2">
         <v>144.2732</v>
       </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
         <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -1238,28 +1056,16 @@
       <c r="I16" s="2">
         <v>181.8</v>
       </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
@@ -1279,28 +1085,16 @@
       <c r="I17" s="2">
         <v>368.4</v>
       </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
@@ -1320,28 +1114,16 @@
       <c r="I18" s="2">
         <v>12.05</v>
       </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -1361,28 +1143,16 @@
       <c r="I19" s="2">
         <v>488.95</v>
       </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -1402,28 +1172,16 @@
       <c r="I20" s="2">
         <v>713.9</v>
       </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -1443,28 +1201,16 @@
       <c r="I21" s="2">
         <v>355.875</v>
       </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
@@ -1484,28 +1230,16 @@
       <c r="I22" s="2">
         <v>581.95000000000005</v>
       </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -1525,28 +1259,16 @@
       <c r="I23" s="2">
         <v>380.25</v>
       </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -1566,28 +1288,16 @@
       <c r="I24" s="2">
         <v>4496.7</v>
       </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0</v>
-      </c>
-      <c r="L24" s="2">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -1607,28 +1317,16 @@
       <c r="I25" s="2">
         <v>137.85</v>
       </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>0</v>
-      </c>
-      <c r="L25" s="2">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -1648,28 +1346,16 @@
       <c r="I26" s="2">
         <v>470.95</v>
       </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -1689,28 +1375,16 @@
       <c r="I27" s="2">
         <v>47.701900000000002</v>
       </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
@@ -1730,28 +1404,16 @@
       <c r="I28" s="2">
         <v>1630.45</v>
       </c>
-      <c r="J28" s="2">
-        <v>0</v>
-      </c>
-      <c r="K28" s="2">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2">
-        <v>0</v>
-      </c>
-      <c r="M28" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -1771,28 +1433,16 @@
       <c r="I29" s="2">
         <v>33.798099999999998</v>
       </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -1812,28 +1462,16 @@
       <c r="I30" s="2">
         <v>1862.5051000000001</v>
       </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -1853,28 +1491,16 @@
       <c r="I31" s="2">
         <v>241.1</v>
       </c>
-      <c r="J31" s="2">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
@@ -1894,28 +1520,16 @@
       <c r="I32" s="2">
         <v>91.444900000000004</v>
       </c>
-      <c r="J32" s="2">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1935,28 +1549,16 @@
       <c r="I33" s="2">
         <v>1295.4628</v>
       </c>
-      <c r="J33" s="2">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D34" s="2">
         <v>1034</v>
@@ -1976,28 +1578,16 @@
       <c r="I34" s="2">
         <v>384.7124</v>
       </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -2017,28 +1607,16 @@
       <c r="I35" s="2">
         <v>381.4</v>
       </c>
-      <c r="J35" s="2">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2">
-        <v>0</v>
-      </c>
-      <c r="M35" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D36" s="2">
         <v>1</v>
@@ -2058,28 +1636,16 @@
       <c r="I36" s="2">
         <v>107.15</v>
       </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D37" s="2">
         <v>1</v>
@@ -2099,28 +1665,16 @@
       <c r="I37" s="2">
         <v>192.55</v>
       </c>
-      <c r="J37" s="2">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2">
-        <v>0</v>
-      </c>
-      <c r="L37" s="2">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D38" s="2">
         <v>1071</v>
@@ -2139,18 +1693,6 @@
       </c>
       <c r="I38" s="2">
         <v>275.80650000000003</v>
-      </c>
-      <c r="J38" s="2">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
